--- a/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_persona_fewshot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_persona_fewshot.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15810,7 +15810,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20706,7 +20706,7 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21216,7 +21216,7 @@
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21624,7 +21624,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -21658,7 +21658,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22202,7 +22202,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22389,7 +22389,7 @@
       </c>
       <c r="C1292" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22780,7 +22780,7 @@
       </c>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23443,7 +23443,7 @@
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24242,7 +24242,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24701,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26265,7 +26265,7 @@
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="C1535" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27115,7 +27115,7 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27217,7 +27217,7 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27659,7 +27659,7 @@
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27693,7 +27693,7 @@
       </c>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27914,7 +27914,7 @@
       </c>
       <c r="C1617" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28016,7 +28016,7 @@
       </c>
       <c r="C1623" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="C1639" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28509,7 +28509,7 @@
       </c>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28764,7 +28764,7 @@
       </c>
       <c r="C1667" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28866,7 +28866,7 @@
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -28900,7 +28900,7 @@
       </c>
       <c r="C1675" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29257,7 +29257,7 @@
       </c>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -29835,7 +29835,7 @@
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -30107,7 +30107,7 @@
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30362,7 +30362,7 @@
       </c>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30413,7 +30413,7 @@
       </c>
       <c r="C1764" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="C1766" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30855,7 +30855,7 @@
       </c>
       <c r="C1790" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -30872,7 +30872,7 @@
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30906,7 +30906,7 @@
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31501,7 +31501,7 @@
       </c>
       <c r="C1828" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31552,7 +31552,7 @@
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31705,7 +31705,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="C1845" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31807,7 +31807,7 @@
       </c>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31875,7 +31875,7 @@
       </c>
       <c r="C1850" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -32011,7 +32011,7 @@
       </c>
       <c r="C1858" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -32096,7 +32096,7 @@
       </c>
       <c r="C1863" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32453,7 +32453,7 @@
       </c>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -32725,7 +32725,7 @@
       </c>
       <c r="C1900" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -32793,7 +32793,7 @@
       </c>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32997,7 +32997,7 @@
       </c>
       <c r="C1916" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33048,7 +33048,7 @@
       </c>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -33116,7 +33116,7 @@
       </c>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -33218,7 +33218,7 @@
       </c>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="C1948" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33728,7 +33728,7 @@
       </c>
       <c r="C1959" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="C1988" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34374,7 +34374,7 @@
       </c>
       <c r="C1997" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34629,7 +34629,7 @@
       </c>
       <c r="C2012" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="C2046" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C2099" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="C2117" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36431,7 +36431,7 @@
       </c>
       <c r="C2118" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="C2119" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36482,7 +36482,7 @@
       </c>
       <c r="C2121" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36533,7 +36533,7 @@
       </c>
       <c r="C2124" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36635,7 +36635,7 @@
       </c>
       <c r="C2130" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36839,7 +36839,7 @@
       </c>
       <c r="C2142" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37179,7 +37179,7 @@
       </c>
       <c r="C2162" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37502,7 +37502,7 @@
       </c>
       <c r="C2181" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37774,7 +37774,7 @@
       </c>
       <c r="C2197" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37927,7 +37927,7 @@
       </c>
       <c r="C2206" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38233,7 +38233,7 @@
       </c>
       <c r="C2224" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38267,7 +38267,7 @@
       </c>
       <c r="C2226" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38335,7 +38335,7 @@
       </c>
       <c r="C2230" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38369,7 +38369,7 @@
       </c>
       <c r="C2232" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38386,7 +38386,7 @@
       </c>
       <c r="C2233" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38454,7 +38454,7 @@
       </c>
       <c r="C2237" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39219,7 +39219,7 @@
       </c>
       <c r="C2282" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39423,7 +39423,7 @@
       </c>
       <c r="C2294" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39457,7 +39457,7 @@
       </c>
       <c r="C2296" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="C2299" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39525,7 +39525,7 @@
       </c>
       <c r="C2300" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39593,7 +39593,7 @@
       </c>
       <c r="C2304" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39712,7 +39712,7 @@
       </c>
       <c r="C2311" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39746,7 +39746,7 @@
       </c>
       <c r="C2313" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40018,7 +40018,7 @@
       </c>
       <c r="C2329" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -40171,7 +40171,7 @@
       </c>
       <c r="C2338" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40409,7 +40409,7 @@
       </c>
       <c r="C2352" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40443,7 +40443,7 @@
       </c>
       <c r="C2354" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40460,7 +40460,7 @@
       </c>
       <c r="C2355" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="C2358" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C2359" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="C2370" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="C2394" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41344,7 +41344,7 @@
       </c>
       <c r="C2407" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41429,7 +41429,7 @@
       </c>
       <c r="C2412" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41633,7 +41633,7 @@
       </c>
       <c r="C2424" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41684,7 +41684,7 @@
       </c>
       <c r="C2427" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41871,7 +41871,7 @@
       </c>
       <c r="C2438" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41956,7 +41956,7 @@
       </c>
       <c r="C2443" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -41990,7 +41990,7 @@
       </c>
       <c r="C2445" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -42381,7 +42381,7 @@
       </c>
       <c r="C2468" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43333,7 +43333,7 @@
       </c>
       <c r="C2524" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43435,7 +43435,7 @@
       </c>
       <c r="C2530" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43469,7 +43469,7 @@
       </c>
       <c r="C2532" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="C2538" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43588,7 +43588,7 @@
       </c>
       <c r="C2539" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43622,7 +43622,7 @@
       </c>
       <c r="C2541" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43690,7 +43690,7 @@
       </c>
       <c r="C2545" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -43945,7 +43945,7 @@
       </c>
       <c r="C2560" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="C2572" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -44540,7 +44540,7 @@
       </c>
       <c r="C2595" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44591,7 +44591,7 @@
       </c>
       <c r="C2598" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="C2601" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
       </c>
       <c r="C2604" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45152,7 +45152,7 @@
       </c>
       <c r="C2631" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -45169,7 +45169,7 @@
       </c>
       <c r="C2632" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -45373,7 +45373,7 @@
       </c>
       <c r="C2644" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="C2663" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46002,7 +46002,7 @@
       </c>
       <c r="C2681" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -46359,7 +46359,7 @@
       </c>
       <c r="C2702" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46461,7 +46461,7 @@
       </c>
       <c r="C2708" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46512,7 +46512,7 @@
       </c>
       <c r="C2711" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -46563,7 +46563,7 @@
       </c>
       <c r="C2714" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -46580,7 +46580,7 @@
       </c>
       <c r="C2715" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46631,7 +46631,7 @@
       </c>
       <c r="C2718" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46716,7 +46716,7 @@
       </c>
       <c r="C2723" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46903,7 +46903,7 @@
       </c>
       <c r="C2734" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47090,7 +47090,7 @@
       </c>
       <c r="C2745" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47209,7 +47209,7 @@
       </c>
       <c r="C2752" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47362,7 +47362,7 @@
       </c>
       <c r="C2761" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47379,7 +47379,7 @@
       </c>
       <c r="C2762" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47481,7 +47481,7 @@
       </c>
       <c r="C2768" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47583,7 +47583,7 @@
       </c>
       <c r="C2774" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47685,7 +47685,7 @@
       </c>
       <c r="C2780" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48161,7 +48161,7 @@
       </c>
       <c r="C2808" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48178,7 +48178,7 @@
       </c>
       <c r="C2809" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48331,7 +48331,7 @@
       </c>
       <c r="C2818" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48416,7 +48416,7 @@
       </c>
       <c r="C2823" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48739,7 +48739,7 @@
       </c>
       <c r="C2842" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48909,7 +48909,7 @@
       </c>
       <c r="C2852" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48977,7 +48977,7 @@
       </c>
       <c r="C2856" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49028,7 +49028,7 @@
       </c>
       <c r="C2859" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49045,7 +49045,7 @@
       </c>
       <c r="C2860" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49130,7 +49130,7 @@
       </c>
       <c r="C2865" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="C2879" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -49436,7 +49436,7 @@
       </c>
       <c r="C2883" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49691,7 +49691,7 @@
       </c>
       <c r="C2898" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49895,7 +49895,7 @@
       </c>
       <c r="C2910" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49963,7 +49963,7 @@
       </c>
       <c r="C2914" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49997,7 +49997,7 @@
       </c>
       <c r="C2916" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50167,7 +50167,7 @@
       </c>
       <c r="C2926" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -50371,7 +50371,7 @@
       </c>
       <c r="C2938" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50405,7 +50405,7 @@
       </c>
       <c r="C2940" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -50711,7 +50711,7 @@
       </c>
       <c r="C2958" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50966,7 @@
       </c>
       <c r="C2973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51017,7 +51017,7 @@
       </c>
       <c r="C2976" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51170,7 +51170,7 @@
       </c>
       <c r="C2985" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51289,7 +51289,7 @@
       </c>
       <c r="C2992" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8223333333333334</v>
+        <v>0.8386666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7338641389286288</v>
+        <v>0.7412304258446586</v>
       </c>
     </row>
     <row r="4">
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8327490109273026</v>
+        <v>0.8458231305707692</v>
       </c>
     </row>
     <row r="5">
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7095645477308622</v>
+        <v>0.7164602588035726</v>
       </c>
     </row>
     <row r="6">
@@ -51519,7 +51519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7777135350583289</v>
+        <v>0.7791845926763372</v>
       </c>
     </row>
     <row r="7">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>752.7120110510004</v>
+        <v>1747.817669266995</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2509040036836668</v>
+        <v>0.582605889755665</v>
       </c>
     </row>
   </sheetData>
